--- a/outputs/daily/hr_rankings_2026-08-11.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-11.xlsx
@@ -8654,34 +8654,30 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13682,7 +13678,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -13707,7 +13703,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 5</t>
+          <t>order MLB 7 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -19278,34 +19274,30 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20950,34 +20942,30 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24582,7 +24570,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -24607,7 +24595,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
+          <t>order MLB 5 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -31274,34 +31262,30 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -32114,7 +32098,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -32139,7 +32123,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
+          <t>order MLB 6 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
